--- a/QCM3_SVT.xlsx
+++ b/QCM3_SVT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WEB_TEST_APP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402E4562-2A23-4EB5-B0DD-50A8C489AB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4B01B5-C761-4B75-9B5C-5DBF763885C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="306">
   <si>
     <t>Question</t>
   </si>
@@ -918,21 +918,35 @@
     <t>Un acide aminé peut être codé par plusieurs codons</t>
   </si>
   <si>
-    <t>La photographie ci-dessous représente une cellule à :
-&lt;img src="/images/SVT_QCM3_Q46.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Le nombre haploïde (n) de cette cellule en division est :
-&lt;img src="/images/SVT_QCM3_Q47.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Le document ci-contre représente le caryotype:
-&lt;img src="/images/SVT_QCM3_Q48.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>SVT_QCM3_Q46.png</t>
+  </si>
+  <si>
+    <t>SVT_QCM3_Q47.png</t>
+  </si>
+  <si>
+    <t>SVT_QCM3_Q48.png</t>
+  </si>
+  <si>
+    <t>SVT_QCM3_Q51.png</t>
   </si>
   <si>
     <t>Le schéma ci-contre représente un processus biologique. 
-&lt;img src="/images/SVT_QCM3_Q51.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 Quelle proposition est correcte à son sujet ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ci-contre représente le caryotype:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La photographie ci-dessous représente une cellule à :
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le nombre haploïde (n) de cette cellule en division est :
+</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1027,6 +1041,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1331,18 +1348,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1368,10 +1385,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>295</v>
       </c>
@@ -1396,8 +1416,9 @@
       <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>295</v>
       </c>
@@ -1422,8 +1443,9 @@
       <c r="H3" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -1448,8 +1470,9 @@
       <c r="H4" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>295</v>
       </c>
@@ -1474,8 +1497,9 @@
       <c r="H5" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>295</v>
       </c>
@@ -1500,8 +1524,9 @@
       <c r="H6" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>295</v>
       </c>
@@ -1526,8 +1551,9 @@
       <c r="H7" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>295</v>
       </c>
@@ -1552,8 +1578,9 @@
       <c r="H8" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>295</v>
       </c>
@@ -1578,8 +1605,9 @@
       <c r="H9" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>295</v>
       </c>
@@ -1604,8 +1632,9 @@
       <c r="H10" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>295</v>
       </c>
@@ -1630,8 +1659,9 @@
       <c r="H11" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>295</v>
       </c>
@@ -1656,8 +1686,9 @@
       <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>295</v>
       </c>
@@ -1682,8 +1713,9 @@
       <c r="H13" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>295</v>
       </c>
@@ -1708,8 +1740,9 @@
       <c r="H14" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>295</v>
       </c>
@@ -1734,8 +1767,9 @@
       <c r="H15" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>295</v>
       </c>
@@ -1760,8 +1794,9 @@
       <c r="H16" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>295</v>
       </c>
@@ -1786,8 +1821,9 @@
       <c r="H17" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>295</v>
       </c>
@@ -1812,8 +1848,9 @@
       <c r="H18" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>295</v>
       </c>
@@ -1838,8 +1875,9 @@
       <c r="H19" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>295</v>
       </c>
@@ -1864,8 +1902,9 @@
       <c r="H20" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>295</v>
       </c>
@@ -1890,8 +1929,9 @@
       <c r="H21" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>295</v>
       </c>
@@ -1916,8 +1956,9 @@
       <c r="H22" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>295</v>
       </c>
@@ -1942,8 +1983,9 @@
       <c r="H23" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>295</v>
       </c>
@@ -1968,8 +2010,9 @@
       <c r="H24" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>295</v>
       </c>
@@ -1994,8 +2037,9 @@
       <c r="H25" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>295</v>
       </c>
@@ -2020,8 +2064,9 @@
       <c r="H26" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>295</v>
       </c>
@@ -2046,8 +2091,9 @@
       <c r="H27" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>295</v>
       </c>
@@ -2072,8 +2118,9 @@
       <c r="H28" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>295</v>
       </c>
@@ -2098,8 +2145,9 @@
       <c r="H29" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>295</v>
       </c>
@@ -2124,8 +2172,9 @@
       <c r="H30" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>295</v>
       </c>
@@ -2150,8 +2199,9 @@
       <c r="H31" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>295</v>
       </c>
@@ -2176,8 +2226,9 @@
       <c r="H32" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>295</v>
       </c>
@@ -2202,8 +2253,9 @@
       <c r="H33" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>295</v>
       </c>
@@ -2228,8 +2280,9 @@
       <c r="H34" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>295</v>
       </c>
@@ -2254,8 +2307,9 @@
       <c r="H35" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>295</v>
       </c>
@@ -2280,8 +2334,9 @@
       <c r="H36" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>295</v>
       </c>
@@ -2306,8 +2361,9 @@
       <c r="H37" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>295</v>
       </c>
@@ -2332,8 +2388,9 @@
       <c r="H38" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>295</v>
       </c>
@@ -2358,8 +2415,9 @@
       <c r="H39" s="4" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>295</v>
       </c>
@@ -2384,8 +2442,9 @@
       <c r="H40" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>295</v>
       </c>
@@ -2410,8 +2469,9 @@
       <c r="H41" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>295</v>
       </c>
@@ -2436,8 +2496,9 @@
       <c r="H42" s="4" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>295</v>
       </c>
@@ -2462,8 +2523,9 @@
       <c r="H43" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>295</v>
       </c>
@@ -2488,8 +2550,9 @@
       <c r="H44" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>295</v>
       </c>
@@ -2514,8 +2577,9 @@
       <c r="H45" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>295</v>
       </c>
@@ -2540,13 +2604,14 @@
       <c r="H46" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -2566,13 +2631,16 @@
       <c r="H47" s="4" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -2590,13 +2658,16 @@
       <c r="H48" s="4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I48" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
@@ -2612,8 +2683,11 @@
       <c r="H49" s="4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I49" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>295</v>
       </c>
@@ -2638,8 +2712,9 @@
       <c r="H50" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>295</v>
       </c>
@@ -2664,13 +2739,14 @@
       <c r="H51" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -2690,8 +2766,11 @@
       <c r="H52" s="4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I52" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>295</v>
       </c>
@@ -2716,8 +2795,9 @@
       <c r="H53" s="4" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>295</v>
       </c>
@@ -2742,8 +2822,9 @@
       <c r="H54" s="4" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>295</v>
       </c>
@@ -2768,8 +2849,9 @@
       <c r="H55" s="4" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>295</v>
       </c>
@@ -2794,8 +2876,9 @@
       <c r="H56" s="4" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>295</v>
       </c>
@@ -2820,8 +2903,9 @@
       <c r="H57" s="4" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>295</v>
       </c>
@@ -2846,8 +2930,9 @@
       <c r="H58" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>295</v>
       </c>
@@ -2872,8 +2957,9 @@
       <c r="H59" s="4" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>295</v>
       </c>
@@ -2898,8 +2984,9 @@
       <c r="H60" s="4" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>295</v>
       </c>
@@ -2924,6 +3011,7 @@
       <c r="H61" s="4" t="s">
         <v>237</v>
       </c>
+      <c r="I61" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM3_SVT.xlsx
+++ b/QCM3_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4B01B5-C761-4B75-9B5C-5DBF763885C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0433A344-A86D-4F3B-BF16-AE28D6309F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -912,9 +912,6 @@
     <t>Quelle partie de l'ARNt se fixe sur l'ARNm</t>
   </si>
   <si>
-    <t>QCM Chapitre 3</t>
-  </si>
-  <si>
     <t>Un acide aminé peut être codé par plusieurs codons</t>
   </si>
   <si>
@@ -933,20 +930,23 @@
     <t>SVT_QCM3_Q51.png</t>
   </si>
   <si>
-    <t>Le schéma ci-contre représente un processus biologique. 
+    <t xml:space="preserve">La photographie ci-dessous représente une cellule à : &lt;img src="/images/SVT_QCM3_Q46.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le nombre haploïde (n) de cette cellule en division est : &lt;img src="/images/SVT_QCM3_Q47.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ci-contre représente le caryotype: &lt;img src="/images/SVT_QCM3_Q48.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t>Le schéma ci-contre représente un processus biologique. &lt;img src="/images/SVT_QCM3_Q51.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 Quelle proposition est correcte à son sujet ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Le document ci-contre représente le caryotype:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La photographie ci-dessous représente une cellule à :
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le nombre haploïde (n) de cette cellule en division est :
-</t>
+    <t>TEST : L'information génétique</t>
   </si>
 </sst>
 </file>
@@ -1385,15 +1385,15 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>241</v>
@@ -1418,9 +1418,9 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>242</v>
@@ -1438,16 +1438,16 @@
         <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>243</v>
@@ -1472,9 +1472,9 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>244</v>
@@ -1499,9 +1499,9 @@
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>245</v>
@@ -1526,9 +1526,9 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>246</v>
@@ -1553,9 +1553,9 @@
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>247</v>
@@ -1580,9 +1580,9 @@
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>248</v>
@@ -1607,9 +1607,9 @@
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>249</v>
@@ -1634,9 +1634,9 @@
       </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>250</v>
@@ -1661,9 +1661,9 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>246</v>
@@ -1688,9 +1688,9 @@
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>251</v>
@@ -1715,9 +1715,9 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>252</v>
@@ -1742,9 +1742,9 @@
       </c>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>253</v>
@@ -1769,9 +1769,9 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>254</v>
@@ -1796,9 +1796,9 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>255</v>
@@ -1823,9 +1823,9 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>256</v>
@@ -1850,9 +1850,9 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>257</v>
@@ -1877,9 +1877,9 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>258</v>
@@ -1904,9 +1904,9 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>259</v>
@@ -1931,9 +1931,9 @@
       </c>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>260</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="23" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>261</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="24" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>262</v>
@@ -2012,9 +2012,9 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>263</v>
@@ -2039,9 +2039,9 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>264</v>
@@ -2066,9 +2066,9 @@
       </c>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>265</v>
@@ -2093,9 +2093,9 @@
       </c>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>266</v>
@@ -2120,9 +2120,9 @@
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>267</v>
@@ -2147,9 +2147,9 @@
       </c>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>268</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="31" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>269</v>
@@ -2201,9 +2201,9 @@
       </c>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>270</v>
@@ -2228,9 +2228,9 @@
       </c>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>271</v>
@@ -2255,9 +2255,9 @@
       </c>
       <c r="I33" s="5"/>
     </row>
-    <row r="34" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>272</v>
@@ -2282,9 +2282,9 @@
       </c>
       <c r="I34" s="5"/>
     </row>
-    <row r="35" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>273</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="36" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>274</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="37" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>275</v>
@@ -2363,9 +2363,9 @@
       </c>
       <c r="I37" s="5"/>
     </row>
-    <row r="38" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>276</v>
@@ -2390,9 +2390,9 @@
       </c>
       <c r="I38" s="5"/>
     </row>
-    <row r="39" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>277</v>
@@ -2417,9 +2417,9 @@
       </c>
       <c r="I39" s="5"/>
     </row>
-    <row r="40" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>278</v>
@@ -2444,9 +2444,9 @@
       </c>
       <c r="I40" s="5"/>
     </row>
-    <row r="41" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>279</v>
@@ -2471,9 +2471,9 @@
       </c>
       <c r="I41" s="5"/>
     </row>
-    <row r="42" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>280</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="43" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>281</v>
@@ -2525,9 +2525,9 @@
       </c>
       <c r="I43" s="5"/>
     </row>
-    <row r="44" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>282</v>
@@ -2552,9 +2552,9 @@
       </c>
       <c r="I44" s="5"/>
     </row>
-    <row r="45" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>283</v>
@@ -2579,9 +2579,9 @@
       </c>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>278</v>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="I46" s="5"/>
     </row>
-    <row r="47" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -2632,15 +2632,15 @@
         <v>188</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -2659,12 +2659,12 @@
         <v>193</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>303</v>
@@ -2684,12 +2684,12 @@
         <v>196</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>284</v>
@@ -2714,9 +2714,9 @@
       </c>
       <c r="I50" s="5"/>
     </row>
-    <row r="51" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>285</v>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="I51" s="5"/>
     </row>
-    <row r="52" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -2767,12 +2767,12 @@
         <v>208</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>286</v>
@@ -2797,9 +2797,9 @@
       </c>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>287</v>
@@ -2824,9 +2824,9 @@
       </c>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>288</v>
@@ -2851,9 +2851,9 @@
       </c>
       <c r="I55" s="5"/>
     </row>
-    <row r="56" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>289</v>
@@ -2878,9 +2878,9 @@
       </c>
       <c r="I56" s="5"/>
     </row>
-    <row r="57" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>290</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="58" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>291</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="59" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>292</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="60" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>293</v>
@@ -2986,9 +2986,9 @@
       </c>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>294</v>
